--- a/test/taille_images.xlsx
+++ b/test/taille_images.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Donnees\IOT\WS_Platformio\Plat_Esp_Camera\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D359FF-C900-4593-9B88-70531FAC823B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34DAFED-458D-4E2B-B504-FFEFFF3C116F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
   <si>
     <t>Size</t>
   </si>
@@ -127,6 +127,36 @@
   </si>
   <si>
     <t>Q60-&gt;46ko  Q28-&gt;13ko</t>
+  </si>
+  <si>
+    <t>code Im</t>
+  </si>
+  <si>
+    <t>24k à 167k</t>
+  </si>
+  <si>
+    <t>13k à 80k</t>
+  </si>
+  <si>
+    <t>9k à 47k</t>
+  </si>
+  <si>
+    <t>5k à 27k</t>
+  </si>
+  <si>
+    <t>5k à 28k</t>
+  </si>
+  <si>
+    <t>1,7k à 6k</t>
+  </si>
+  <si>
+    <t>1k à 3k</t>
+  </si>
+  <si>
+    <t>Qualité</t>
+  </si>
+  <si>
+    <t>en 1600*1200</t>
   </si>
 </sst>
 </file>
@@ -145,12 +175,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -165,11 +207,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -450,1004 +494,1311 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:N48"/>
+  <dimension ref="A4:O69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="8.88671875" style="2"/>
-    <col min="4" max="4" width="13.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="8.88671875" style="2"/>
-    <col min="13" max="13" width="8.88671875" style="2"/>
-    <col min="14" max="14" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="8.88671875" style="2"/>
+    <col min="5" max="5" width="13.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.88671875" style="2"/>
+    <col min="14" max="14" width="8.88671875" style="2"/>
+    <col min="15" max="15" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>1</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C5" s="2" t="s">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>7</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2048</v>
       </c>
       <c r="B6">
         <v>1536</v>
       </c>
-      <c r="C6" s="2">
+      <c r="D6" s="2">
         <f>B6*A6/100000</f>
         <v>31.457280000000001</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E6" s="2">
         <v>100</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2048</v>
       </c>
       <c r="B7">
         <v>1536</v>
       </c>
-      <c r="C7" s="2">
-        <f>C6</f>
+      <c r="D7" s="2">
+        <f>D6</f>
         <v>31.457280000000001</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E7" s="2">
         <v>60</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>10</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>181.2</v>
       </c>
-      <c r="G7" s="2">
-        <f>C7/E7*70</f>
+      <c r="H7" s="2">
+        <f>D7/F7*70</f>
         <v>220.20096000000001</v>
       </c>
-      <c r="H7" s="1">
-        <f>G7/G19</f>
+      <c r="I7" s="1">
+        <f>H7/H19</f>
         <v>3.84</v>
       </c>
-      <c r="M7" s="2">
-        <f>A7*B7/8*(0.15+2.4*(D7/100)^2)</f>
+      <c r="N7" s="2">
+        <f>A7*B7/8*(0.15+2.4*(E7/100)^2)</f>
         <v>398721.02399999998</v>
       </c>
-      <c r="N7" s="1">
-        <f>M7/F7/1000</f>
+      <c r="O7" s="1">
+        <f>N7/G7/1000</f>
         <v>2.200447152317881</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2048</v>
       </c>
       <c r="B8">
         <v>1536</v>
       </c>
-      <c r="C8" s="2">
-        <f>C7</f>
+      <c r="D8" s="2">
+        <f>D7</f>
         <v>31.457280000000001</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E8" s="2">
         <v>30</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>14</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>141.69999999999999</v>
       </c>
-      <c r="G8" s="2">
-        <f>C8/E8*70</f>
+      <c r="H8" s="2">
+        <f>D8/F8*70</f>
         <v>157.28639999999999</v>
       </c>
-      <c r="H8" s="1">
-        <f>G8/G20</f>
+      <c r="I8" s="1">
+        <f>H8/H20</f>
         <v>3.8399999999999994</v>
       </c>
-      <c r="M8" s="2">
-        <f t="shared" ref="M8:M26" si="0">A8*B8/8*(0.15+2.4*(D8/100)^2)</f>
+      <c r="N8" s="2">
+        <f t="shared" ref="N8:N26" si="0">A8*B8/8*(0.15+2.4*(E8/100)^2)</f>
         <v>143917.05599999998</v>
       </c>
-      <c r="N8" s="1">
-        <f t="shared" ref="N8:N26" si="1">M8/F8/1000</f>
+      <c r="O8" s="1">
+        <f t="shared" ref="O8:O26" si="1">N8/G8/1000</f>
         <v>1.0156461256175018</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2048</v>
       </c>
       <c r="B9">
         <v>1536</v>
       </c>
-      <c r="C9" s="2">
-        <f>C8</f>
+      <c r="D9" s="2">
+        <f>D8</f>
         <v>31.457280000000001</v>
       </c>
-      <c r="D9" s="2">
+      <c r="E9" s="2">
         <v>10</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>63</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>67.7</v>
       </c>
-      <c r="G9" s="2">
-        <f>C9/E9*70</f>
+      <c r="H9" s="2">
+        <f>D9/F9*70</f>
         <v>34.952533333333335</v>
       </c>
-      <c r="H9" s="1">
-        <f>G9/G17</f>
+      <c r="I9" s="1">
+        <f>H9/H17</f>
         <v>2.56</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>12</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>21</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>31</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>42</v>
       </c>
-      <c r="M9" s="2">
+      <c r="N9" s="2">
         <f t="shared" si="0"/>
         <v>68419.584000000003</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <f t="shared" si="1"/>
         <v>1.0106290103397342</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1600</v>
       </c>
       <c r="B10">
         <v>1200</v>
       </c>
-      <c r="C10" s="2">
+      <c r="D10" s="2">
         <f>B10*A10/100000</f>
         <v>19.2</v>
       </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <v>100</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>4</v>
       </c>
-      <c r="M10" s="2">
+      <c r="N10" s="2">
         <f t="shared" si="0"/>
         <v>612000</v>
       </c>
-      <c r="N10" s="1" t="e">
+      <c r="O10" s="1" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1600</v>
       </c>
       <c r="B11">
         <v>1200</v>
       </c>
-      <c r="C11" s="2">
-        <f>C10</f>
+      <c r="D11" s="2">
+        <f>D10</f>
         <v>19.2</v>
       </c>
-      <c r="D11" s="2">
+      <c r="E11" s="2">
         <v>60</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>10</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>157.69999999999999</v>
       </c>
-      <c r="G11" s="2">
-        <f t="shared" ref="G11:G26" si="2">C11/E11*70</f>
+      <c r="H11" s="2">
+        <f t="shared" ref="H11:H26" si="2">D11/F11*70</f>
         <v>134.4</v>
       </c>
-      <c r="M11" s="2">
+      <c r="N11" s="2">
         <f t="shared" si="0"/>
         <v>243360</v>
       </c>
-      <c r="N11" s="1">
+      <c r="O11" s="1">
         <f t="shared" si="1"/>
         <v>1.5431832593532024</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1600</v>
       </c>
       <c r="B12">
         <v>1200</v>
       </c>
-      <c r="C12" s="2">
-        <f>C11</f>
+      <c r="D12" s="2">
+        <f>D11</f>
         <v>19.2</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E12" s="2">
         <v>30</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>14</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>88.5</v>
       </c>
-      <c r="G12" s="2">
+      <c r="H12" s="2">
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
-      <c r="M12" s="2">
+      <c r="N12" s="2">
         <f t="shared" si="0"/>
         <v>87840</v>
       </c>
-      <c r="N12" s="1">
+      <c r="O12" s="1">
         <f t="shared" si="1"/>
         <v>0.99254237288135594</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1600</v>
       </c>
       <c r="B13">
         <v>1200</v>
       </c>
-      <c r="C13" s="2">
-        <f>C12</f>
+      <c r="D13" s="2">
+        <f>D12</f>
         <v>19.2</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E13" s="2">
         <v>10</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>63</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>42.5</v>
       </c>
-      <c r="G13" s="2">
+      <c r="H13" s="2">
         <f t="shared" si="2"/>
         <v>21.333333333333332</v>
       </c>
-      <c r="M13" s="2">
+      <c r="N13" s="2">
         <f t="shared" si="0"/>
         <v>41760</v>
       </c>
-      <c r="N13" s="1">
+      <c r="O13" s="1">
         <f t="shared" si="1"/>
         <v>0.98258823529411765</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1200</v>
       </c>
       <c r="B14">
         <v>1024</v>
       </c>
-      <c r="C14" s="2">
+      <c r="D14" s="2">
         <f>B14*A14/100000</f>
         <v>12.288</v>
       </c>
-      <c r="D14" s="2">
+      <c r="E14" s="2">
         <v>100</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>4</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>201.7</v>
       </c>
-      <c r="G14" s="2">
+      <c r="H14" s="2">
         <f t="shared" si="2"/>
         <v>215.04</v>
       </c>
-      <c r="M14" s="2">
+      <c r="N14" s="2">
         <f t="shared" si="0"/>
         <v>391680</v>
       </c>
-      <c r="N14" s="1">
+      <c r="O14" s="1">
         <f t="shared" si="1"/>
         <v>1.9418939018344077</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1200</v>
       </c>
       <c r="B15">
         <v>1024</v>
       </c>
-      <c r="C15" s="2">
-        <f t="shared" ref="C15:C17" si="3">C14</f>
+      <c r="D15" s="2">
+        <f t="shared" ref="D15:D17" si="3">D14</f>
         <v>12.288</v>
       </c>
-      <c r="D15" s="2">
+      <c r="E15" s="2">
         <v>65</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>8</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>117.7</v>
       </c>
-      <c r="G15" s="2">
+      <c r="H15" s="2">
         <f t="shared" si="2"/>
         <v>107.52</v>
       </c>
-      <c r="M15" s="2">
+      <c r="N15" s="2">
         <f t="shared" si="0"/>
         <v>178790.39999999999</v>
       </c>
-      <c r="N15" s="1">
+      <c r="O15" s="1">
         <f t="shared" si="1"/>
         <v>1.5190348343245539</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1200</v>
       </c>
       <c r="B16">
         <v>1024</v>
       </c>
-      <c r="C16" s="2">
+      <c r="D16" s="2">
         <f t="shared" si="3"/>
         <v>12.288</v>
       </c>
-      <c r="D16" s="2">
+      <c r="E16" s="2">
         <v>30</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>14</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>59.7</v>
       </c>
-      <c r="G16" s="2">
+      <c r="H16" s="2">
         <f t="shared" si="2"/>
         <v>61.440000000000005</v>
       </c>
-      <c r="M16" s="2">
+      <c r="N16" s="2">
         <f t="shared" si="0"/>
         <v>56217.599999999999</v>
       </c>
-      <c r="N16" s="1">
+      <c r="O16" s="1">
         <f t="shared" si="1"/>
         <v>0.94166834170854274</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1200</v>
       </c>
       <c r="B17">
         <v>1024</v>
       </c>
-      <c r="C17" s="2">
+      <c r="D17" s="2">
         <f t="shared" si="3"/>
         <v>12.288</v>
       </c>
-      <c r="D17" s="2">
+      <c r="E17" s="2">
         <v>10</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>63</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>30</v>
       </c>
-      <c r="G17" s="2">
+      <c r="H17" s="2">
         <f t="shared" si="2"/>
         <v>13.653333333333334</v>
       </c>
-      <c r="M17" s="2">
+      <c r="N17" s="2">
         <f t="shared" si="0"/>
         <v>26726.399999999998</v>
       </c>
-      <c r="N17" s="1">
+      <c r="O17" s="1">
         <f t="shared" si="1"/>
         <v>0.89087999999999989</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1024</v>
       </c>
       <c r="B18">
         <v>800</v>
       </c>
-      <c r="C18" s="2">
+      <c r="D18" s="2">
         <f>B18*A18/100000</f>
         <v>8.1920000000000002</v>
       </c>
-      <c r="D18" s="2">
+      <c r="E18" s="2">
         <v>100</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>4</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>48.3</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18" s="2">
         <f t="shared" si="2"/>
         <v>143.36000000000001</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>11</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>20</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>30</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>41</v>
       </c>
-      <c r="M18" s="2">
+      <c r="N18" s="2">
         <f t="shared" si="0"/>
         <v>261119.99999999997</v>
       </c>
-      <c r="N18" s="1">
+      <c r="O18" s="1">
         <f t="shared" si="1"/>
         <v>5.4062111801242239</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1024</v>
       </c>
       <c r="B19">
         <v>800</v>
       </c>
-      <c r="C19" s="2">
-        <f t="shared" ref="C19:C22" si="4">C18</f>
+      <c r="D19" s="2">
+        <f t="shared" ref="D19:D22" si="4">D18</f>
         <v>8.1920000000000002</v>
       </c>
-      <c r="D19" s="2">
+      <c r="E19" s="2">
         <v>60</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>10</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>33.6</v>
       </c>
-      <c r="G19" s="2">
+      <c r="H19" s="2">
         <f t="shared" si="2"/>
         <v>57.344000000000001</v>
       </c>
-      <c r="M19" s="2">
+      <c r="N19" s="2">
         <f t="shared" si="0"/>
         <v>103833.60000000001</v>
       </c>
-      <c r="N19" s="1">
+      <c r="O19" s="1">
         <f t="shared" si="1"/>
         <v>3.0902857142857143</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1024</v>
       </c>
       <c r="B20">
         <v>800</v>
       </c>
-      <c r="C20" s="2">
+      <c r="D20" s="2">
         <f t="shared" si="4"/>
         <v>8.1920000000000002</v>
       </c>
-      <c r="D20" s="2">
+      <c r="E20" s="2">
         <v>30</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>14</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>29.6</v>
       </c>
-      <c r="G20" s="2">
+      <c r="H20" s="2">
         <f t="shared" si="2"/>
         <v>40.96</v>
       </c>
-      <c r="M20" s="2">
+      <c r="N20" s="2">
         <f t="shared" si="0"/>
         <v>37478.400000000001</v>
       </c>
-      <c r="N20" s="1">
+      <c r="O20" s="1">
         <f t="shared" si="1"/>
         <v>1.2661621621621622</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1024</v>
       </c>
       <c r="B21">
         <v>800</v>
       </c>
-      <c r="C21" s="2">
+      <c r="D21" s="2">
         <f t="shared" si="4"/>
         <v>8.1920000000000002</v>
       </c>
-      <c r="D21" s="2">
+      <c r="E21" s="2">
         <v>20</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>32</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>20.3</v>
       </c>
-      <c r="G21" s="2">
+      <c r="H21" s="2">
         <f t="shared" si="2"/>
         <v>17.920000000000002</v>
       </c>
-      <c r="M21" s="2">
+      <c r="N21" s="2">
         <f t="shared" si="0"/>
         <v>25190.400000000001</v>
       </c>
-      <c r="N21" s="1">
+      <c r="O21" s="1">
         <f t="shared" si="1"/>
         <v>1.2409064039408868</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1024</v>
       </c>
       <c r="B22">
         <v>800</v>
       </c>
-      <c r="C22" s="2">
+      <c r="D22" s="2">
         <f t="shared" si="4"/>
         <v>8.1920000000000002</v>
       </c>
-      <c r="D22" s="2">
+      <c r="E22" s="2">
         <v>10</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>63</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>17.5</v>
       </c>
-      <c r="G22" s="2">
+      <c r="H22" s="2">
         <f t="shared" si="2"/>
         <v>9.1022222222222222</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>9</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>19</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>28</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>39</v>
       </c>
-      <c r="M22" s="2">
+      <c r="N22" s="2">
         <f t="shared" si="0"/>
         <v>17817.599999999999</v>
       </c>
-      <c r="N22" s="1">
+      <c r="O22" s="1">
         <f t="shared" si="1"/>
         <v>1.0181485714285714</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>800</v>
       </c>
       <c r="B23">
         <v>600</v>
       </c>
-      <c r="C23" s="2">
+      <c r="D23" s="2">
         <f>B23*A23/100000</f>
         <v>4.8</v>
       </c>
-      <c r="D23" s="2">
+      <c r="E23" s="2">
         <v>100</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>4</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>65.5</v>
       </c>
-      <c r="G23" s="2">
+      <c r="H23" s="2">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>32</v>
       </c>
-      <c r="M23" s="2">
+      <c r="N23" s="2">
         <f t="shared" si="0"/>
         <v>153000</v>
       </c>
-      <c r="N23" s="1">
+      <c r="O23" s="1">
         <f t="shared" si="1"/>
         <v>2.3358778625954195</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>800</v>
       </c>
       <c r="B24">
         <v>600</v>
       </c>
-      <c r="C24" s="2">
+      <c r="D24" s="2">
         <f>B24*A24/100000</f>
         <v>4.8</v>
       </c>
-      <c r="D24" s="2">
+      <c r="E24" s="2">
         <v>72</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>11</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>34</v>
       </c>
-      <c r="G24" s="2">
+      <c r="H24" s="2">
         <f t="shared" si="2"/>
         <v>30.545454545454543</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>33</v>
       </c>
-      <c r="M24" s="2">
+      <c r="N24" s="2">
         <f t="shared" si="0"/>
         <v>83649.599999999991</v>
       </c>
-      <c r="N24" s="1">
+      <c r="O24" s="1">
         <f t="shared" si="1"/>
         <v>2.4602823529411761</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>800</v>
       </c>
       <c r="B25">
         <v>600</v>
       </c>
-      <c r="D25" s="2">
+      <c r="E25" s="2">
         <v>54</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>26</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>21.1</v>
       </c>
-      <c r="M25" s="2">
+      <c r="N25" s="2">
         <f t="shared" si="0"/>
         <v>50990.400000000001</v>
       </c>
-      <c r="N25" s="1">
+      <c r="O25" s="1">
         <f t="shared" si="1"/>
         <v>2.4166066350710897</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>800</v>
       </c>
       <c r="B26">
         <v>600</v>
       </c>
-      <c r="C26" s="2">
-        <f>C23</f>
+      <c r="D26" s="2">
+        <f>D23</f>
         <v>4.8</v>
       </c>
-      <c r="D26" s="2">
+      <c r="E26" s="2">
         <v>5</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>63</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>15</v>
       </c>
-      <c r="G26" s="2">
+      <c r="H26" s="2">
         <f t="shared" si="2"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>9</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>18</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>28</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>39</v>
       </c>
-      <c r="M26" s="2">
+      <c r="N26" s="2">
         <f t="shared" si="0"/>
         <v>9360</v>
       </c>
-      <c r="N26" s="1">
+      <c r="O26" s="1">
         <f t="shared" si="1"/>
         <v>0.624</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="I32" t="s">
-        <v>27</v>
-      </c>
-      <c r="J32" t="s">
-        <v>24</v>
-      </c>
-      <c r="K32" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>28</v>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>2560</v>
+      </c>
+      <c r="B29">
+        <v>1920</v>
+      </c>
+      <c r="C29">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>2048</v>
+      </c>
+      <c r="B30">
+        <v>1536</v>
+      </c>
+      <c r="C30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>1600</v>
+      </c>
+      <c r="B31">
+        <v>1200</v>
+      </c>
+      <c r="C31">
+        <v>7</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="2">
+        <f>A31*B31/10000</f>
+        <v>192</v>
+      </c>
+      <c r="F31" s="1">
+        <f>E31/E32</f>
+        <v>1.46484375</v>
+      </c>
+      <c r="H31" s="2">
+        <f>167/24</f>
+        <v>6.958333333333333</v>
+      </c>
+      <c r="I31" s="2">
+        <f>167/47</f>
+        <v>3.5531914893617023</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>1280</v>
+      </c>
+      <c r="B32">
+        <v>1024</v>
+      </c>
+      <c r="C32">
+        <v>6</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="2">
+        <f t="shared" ref="E32:E38" si="5">A32*B32/10000</f>
+        <v>131.072</v>
+      </c>
+      <c r="F32" s="1">
+        <f t="shared" ref="F32:F37" si="6">E32/E33</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="H32" s="2">
+        <f>80/13</f>
+        <v>6.1538461538461542</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>1024</v>
+      </c>
+      <c r="B33">
+        <v>768</v>
+      </c>
+      <c r="C33">
+        <v>5</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>5</v>
-      </c>
-      <c r="J33" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="E33" s="2">
+        <f t="shared" si="5"/>
+        <v>78.643199999999993</v>
+      </c>
+      <c r="F33" s="1">
+        <f t="shared" si="6"/>
+        <v>1.6383999999999999</v>
+      </c>
+      <c r="H33" s="2">
+        <f>47/8</f>
+        <v>5.875</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>800</v>
       </c>
       <c r="B34">
         <v>600</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="2">
+        <f>A34*B34/10000</f>
+        <v>48</v>
+      </c>
+      <c r="F34" s="1">
+        <f t="shared" si="6"/>
+        <v>1.5625</v>
+      </c>
+      <c r="H34" s="2">
+        <f>27/5</f>
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>640</v>
+      </c>
+      <c r="B35">
+        <v>480</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="2">
+        <f t="shared" si="5"/>
+        <v>30.72</v>
+      </c>
+      <c r="F35" s="1">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>480</v>
+      </c>
+      <c r="B36">
+        <v>320</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="E36" s="2">
+        <f t="shared" si="5"/>
+        <v>15.36</v>
+      </c>
+      <c r="F36" s="1">
+        <f t="shared" si="6"/>
+        <v>3.6363636363636362</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>240</v>
+      </c>
+      <c r="B37">
+        <v>176</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="2">
+        <f t="shared" si="5"/>
+        <v>4.2240000000000002</v>
+      </c>
+      <c r="F37" s="1">
+        <f t="shared" si="6"/>
+        <v>4.5833333333333339</v>
+      </c>
+      <c r="H37" s="2">
+        <f>6/1.7</f>
+        <v>3.5294117647058822</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>96</v>
+      </c>
+      <c r="B38">
+        <v>96</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="2">
+        <f t="shared" si="5"/>
+        <v>0.92159999999999997</v>
+      </c>
+      <c r="H38" s="2">
+        <f>3/1</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B42">
+        <v>7</v>
+      </c>
+      <c r="C42">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B43">
+        <v>11</v>
+      </c>
+      <c r="C43">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B44">
+        <v>17</v>
+      </c>
+      <c r="C44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B45">
+        <v>24</v>
+      </c>
+      <c r="C45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="4">
+        <v>32</v>
+      </c>
+      <c r="C46" s="4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B47" s="5">
+        <v>43</v>
+      </c>
+      <c r="C47" s="5">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B48">
+        <v>56</v>
+      </c>
+      <c r="C48">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B49">
+        <v>63</v>
+      </c>
+      <c r="C49">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J53" t="s">
+        <v>27</v>
+      </c>
+      <c r="K53" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F54" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" t="s">
+        <v>5</v>
+      </c>
+      <c r="K54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>800</v>
+      </c>
+      <c r="B55">
+        <v>600</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F55" t="s">
         <v>22</v>
       </c>
-      <c r="F34">
+      <c r="G55">
         <v>32110</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G35" s="2" t="s">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H56" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="I56" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I35">
+      <c r="J56">
         <v>40</v>
       </c>
-      <c r="J35">
+      <c r="K56">
         <v>10160</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G36" s="2" t="s">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H57" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="I57" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I36">
+      <c r="J57">
         <v>40</v>
       </c>
-      <c r="J36">
+      <c r="K57">
         <v>17230</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G37" s="2" t="s">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H58" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="I58" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I37">
+      <c r="J58">
         <v>40</v>
       </c>
-      <c r="J37">
+      <c r="K58">
         <v>22420</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G38" s="2" t="s">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H59" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="I59" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I38">
+      <c r="J59">
         <v>40</v>
       </c>
-      <c r="J38">
+      <c r="K59">
         <v>3240</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G39" s="2" t="s">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H60" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="I60" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I39">
+      <c r="J60">
         <v>65</v>
       </c>
-      <c r="J39">
+      <c r="K60">
         <v>21040</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G40" s="2" t="s">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="I61" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I40">
+      <c r="J61">
         <v>77</v>
       </c>
-      <c r="J40">
+      <c r="K61">
         <v>36800</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G41" s="2" t="s">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H62" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="I62" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I41">
+      <c r="J62">
         <v>82</v>
       </c>
-      <c r="J41">
+      <c r="K62">
         <v>57000</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63">
         <v>1600</v>
       </c>
-      <c r="B42">
+      <c r="B63">
         <v>1200</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="E63" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F63" t="s">
         <v>23</v>
       </c>
-      <c r="F42">
+      <c r="G63">
         <v>95710</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="H63" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="I63" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I42">
+      <c r="J63">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G43" s="2" t="s">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H64" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="I64" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I43">
+      <c r="J64">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G44" s="2" t="s">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H65" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="I65" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H45" s="2" t="s">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I66" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I45">
+      <c r="J66">
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H46" s="2" t="s">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I67" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I46">
+      <c r="J67">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68">
         <v>800</v>
       </c>
-      <c r="B47">
+      <c r="B68">
         <v>600</v>
       </c>
-      <c r="C47" s="2">
+      <c r="D68" s="2">
         <v>36</v>
       </c>
-      <c r="D47" s="2">
+      <c r="E68" s="2">
         <v>44</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F68" t="s">
         <v>30</v>
       </c>
-      <c r="F47">
+      <c r="G68">
         <v>13260</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G48" s="2" t="s">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H69" s="2" t="s">
         <v>31</v>
       </c>
     </row>
